--- a/01_Gestion/cronograma ATLEKTRONIK semestre 2026-1.xlsx
+++ b/01_Gestion/cronograma ATLEKTRONIK semestre 2026-1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JUAN PABLO\OneDrive\Documentos\UNIVERSIDAD (SEPTIMO SEMESTRE) VII\proyecto CDIO 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JUAN PABLO\OneDrive\Documentos\GitHub\CDIO3_Eq-4-_Atlektronik\01_Gestion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E53DE874-4818-4C18-99E3-69B5A92C4AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{844DF413-F99B-4EA2-B8E7-B724D6B7015E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C443CA2-D043-4F85-82C8-F0F522B72D71}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>Tipo de Tarea</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Prueba</t>
   </si>
   <si>
-    <t>validar la calibracion de la celda de carga y comprobar el funcionamiento del cirucuito ADC y amplificador</t>
-  </si>
-  <si>
     <t>salida de señal que llega al microcontrolador amplificada y digital</t>
   </si>
   <si>
@@ -83,18 +80,12 @@
     <t>La pantalla actualiza los valores de fuerza de manera estable.</t>
   </si>
   <si>
-    <t>Semana 8 u 9</t>
-  </si>
-  <si>
     <t>Someter la estructura de la pera a impactos controlados para verificar que no existan vibraciones.</t>
   </si>
   <si>
     <t>El mecanismo se desplaza en su eje y regresa a su posición inicial.</t>
   </si>
   <si>
-    <t>Semana 10 y 11</t>
-  </si>
-  <si>
     <t>Diseño</t>
   </si>
   <si>
@@ -119,29 +110,47 @@
     <t>diseño y prueba</t>
   </si>
   <si>
-    <t>crear mediante codigos de programación la base de datos de los usuarios para registrar su historico de datos</t>
-  </si>
-  <si>
     <t>archivo compilado que permita actualizar datos sin errores.</t>
   </si>
   <si>
     <t>semana 13 y 14</t>
   </si>
   <si>
-    <t>implementar el sistema de sensado, visualización y circuiteria general en la carcasa principal</t>
-  </si>
-  <si>
     <t>producto terminado y listo para ser probado</t>
   </si>
   <si>
     <t>semana 14 y 15</t>
+  </si>
+  <si>
+    <t>validar la calibracion de la celda de carga (con una de menor capacidad y luego con la requerida para el proyecto) y comprobar el funcionamiento del cirucuito ADC y amplificador</t>
+  </si>
+  <si>
+    <t>Semana 11 u 12</t>
+  </si>
+  <si>
+    <t>Semana 9 y 10</t>
+  </si>
+  <si>
+    <t>crear mediante codigos de programación la base de datos de los usuarios para registrar su historico de datos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">implementar el sistema de sensado, visualización y circuiteria en pcb general en la carcasa principal para finalizar el producto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">prueba </t>
+  </si>
+  <si>
+    <t xml:space="preserve">realizar a medida todo el protocolo de pruebas, para corrobar que el sistema envie datos reles y que los impactos no descalibren el sensor o la visualizacion en la pantalla </t>
+  </si>
+  <si>
+    <t>protocolo de pruebas finalizado para poder dejar el prototipo listo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,7 +201,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -365,11 +374,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -405,6 +449,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -741,8 +794,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88EB4423-5F21-42C2-8E5F-F83A99F92837}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="46.33203125" customWidth="1"/>
     <col min="2" max="2" width="56.6640625" customWidth="1"/>
@@ -750,7 +803,7 @@
     <col min="4" max="4" width="67.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -764,7 +817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="73.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="73.8" customHeight="1" thickBot="1">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -778,102 +831,116 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="78" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="78" customHeight="1" thickBot="1">
       <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="4" spans="1:4" ht="78.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="78.599999999999994" customHeight="1" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="76.2" customHeight="1" thickBot="1">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="69.599999999999994" customHeight="1" thickBot="1">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" spans="1:4" ht="69.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="7" spans="1:4" ht="96" customHeight="1" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D7" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="8" t="s">
+    <row r="8" spans="1:4" ht="90" customHeight="1" thickBot="1">
+      <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="B8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D8" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+    <row r="9" spans="1:4" ht="90" customHeight="1" thickBot="1">
+      <c r="A9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="73.2" customHeight="1" thickBot="1">
+      <c r="A10" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="D10" s="12" t="s">
         <v>26</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="73.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
